--- a/it23212022- Test cases.xlsx
+++ b/it23212022- Test cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MSII\Desktop\IT23212022\test_automation\test_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02427E2A-593B-413A-A922-BE0FBC9800A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5FC51A-FF5D-4F77-A995-184FEDBF5D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="286">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -650,13 +650,2104 @@
   </si>
   <si>
     <t>Evidence or rationale</t>
+  </si>
+  <si>
+    <t>Question forms</t>
+  </si>
+  <si>
+    <t>Greetings</t>
+  </si>
+  <si>
+    <t>Requests</t>
+  </si>
+  <si>
+    <t>Romanization / Spelling Variants</t>
+  </si>
+  <si>
+    <t>Inputs Containing Emojis</t>
+  </si>
+  <si>
+    <t>Multi-Word English Phrases in Singlish</t>
+  </si>
+  <si>
+    <t>Command forms</t>
+  </si>
+  <si>
+    <t>Platform/App Names in Singlish</t>
+  </si>
+  <si>
+    <t>Person Names Embedded in Singlish</t>
+  </si>
+  <si>
+    <t>Inputs with Numbers and Numeric Suffixes</t>
+  </si>
+  <si>
+    <t>Repeated Words</t>
+  </si>
+  <si>
+    <t>Inputs with Unit of Measurements</t>
+  </si>
+  <si>
+    <t>Inputs with Punctuation Marks</t>
+  </si>
+  <si>
+    <t>Online Indentifiers in Singlish</t>
+  </si>
+  <si>
+    <t>Responses</t>
+  </si>
+  <si>
+    <t>English Abbreviations/Acronyms in Singlish</t>
+  </si>
+  <si>
+    <t>Place Names Embedded in Singlish</t>
+  </si>
+  <si>
+    <t>Isolated English Word Insertions in Singlish</t>
+  </si>
+  <si>
+    <t>English Digital Terms in Singlish</t>
+  </si>
+  <si>
+    <t>Slang and Casual Phrasing</t>
+  </si>
+  <si>
+    <t>Inputs with Dates</t>
+  </si>
+  <si>
+    <t>English Clipped Forms in Singlish</t>
+  </si>
+  <si>
+    <t>Inputs with Currency</t>
+  </si>
+  <si>
+    <t>Inputs with Time Formats</t>
+  </si>
+  <si>
+    <t>Inputs with Country</t>
+  </si>
+  <si>
+    <t>English  Terms in Singlish</t>
+  </si>
+  <si>
+    <t>Evidence: "🎇👔🖼🖼🕶🧤🧦🧥👛;):-P:P:(👗🧣⛳💄"
+Rationale: The input contains multiple emojis and emoticons.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "monatada aave?"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>: The overall message is a question.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "suba sandawak!"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> The phrase is used as a greeting wishing a good evening.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">: "kibulaa"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> The word is a spelling variant / specific romanization for 'කිඹුලා'.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "oya google form eka submit karala danna"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> The entire sentence functions as a request to perform an action.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "dskvfj vomj vdhnj lkm"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rationale: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>The input consists entirely of random keyboard mashing, representing non-standard spelling variants.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "really good"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rationale: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Two consecutive English words are inserted inside the Singlish input.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "📼"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> The input contains an emoji at the end.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "OYA DANNA MAGULAK NAHA"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> The entire phrase is a casual/slang expression used to shut down a conversation.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Evidence: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"Facebook"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> The input includes the name of a social media platform.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "AWILLA DUWANNA"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> The phrase is an explicit command telling someone to run.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Evidence: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"subha subha"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> The word 'subha' is repeated consecutively.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "Km 2i, Kilometre 3i, kilometer 4i, adi 3i feet 2i"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rationale: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Includes units of measurements like 'Km' and 'adi' alongside numeric values.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "," and "."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> The input uses specific punctuation marks like commas and periods.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "naththalmaasedecember"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> The words are concatenated together without spaces, representing a spelling variant.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "oba siyalu denatama pin siddavei"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> A traditional phrase used as a formal response/blessing.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "Ricky Jason Vanderheyden"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Includes a full English person name embedded in the text.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Evidence: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"ID"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rationale: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Contains the English acronym 'ID' (Identification Document).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "chair"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> A single English word is inserted into the Singlish sentence.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "unam monawa wunath hoda yaluwek"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rationale: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Functions as a response/reply affirming someone's character.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "Roman Numbers"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Refers to a specific English digital/numeric term system.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "nuwaraeliye"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Includes a specific local place name embedded in the text.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "kala wawen"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rationale: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Mentions a specific geographic location/place name.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "ado eka nm patta wasi"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> The sentence heavily relies on casual slang phrasing ('ado', 'patta').</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "Angel"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rationale: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>A single English word inserted directly into the Singlish.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "dollar 100"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Expresses a specific monetary currency value.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "full-athel"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Uses a clipped/modified English form mixed with slang.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "7:30AM"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Specifies a clear time format with AM/PM.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "italiye"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rationale: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>The place name 'Italy' is embedded and localized.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "IP address"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Uses an English digital/networking term.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "kilomitara 5k"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Combines a unit of measurement with a numeric value.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "8.00AM", "5.00PM"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Includes explicit time format ranges.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "aaddareee"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Rationale: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>The word uses repeated letters to express emphasis as a spelling variant.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "Monkey pox"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Inserts a multi-word English medical phrase.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "santhawarun palliyata giyeya irida poojawata."
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Context acts as a formal narrative or response regarding a church visit.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "oyata exam eka shape da machchan mchn"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> The overall sentence is a question.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "msg"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Uses 'msg' as a clipped form for the English word 'message'.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "B.C 1900"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Includes a specific historical date/era format.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "doenets.lk"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Contains a specific domain name/online identifier.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Evidence: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"Aney!"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Uses an exclamation mark for emphasis.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "soap2day.com"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Includes a specific website URL, which is an online identifier.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Evidence: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"kumudu's"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Includes the specific name of a person embedded within the Singlish text.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "honda", "wada"
+R</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">ationale: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>The words use specific non-standard romanized spelling variants.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Evidence: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"mata can't ane owa karanna!"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> The phrase functions as a request or plea to not do something.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "3weni"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Uses a number (3) combined with a numeric suffix (weni) to indicate position.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Evidence: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"america"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> The name of a country/place is embedded in the Singlish text.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Evidence: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"IAS"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Includes the English abbreviation/acronym 'IAS'.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Evidence: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"Mr.Perera"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Embeds a person's name with a title in the text.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Evidence: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">"Government School"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Contains a clipped standard English term embedded in the text.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Evidence:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> "feeling very sad today"
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Rationale:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> A continuous multi-word English phrase is inserted.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -688,6 +2779,12 @@
       <color theme="1"/>
       <name val="Iskoola Pota"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8.5"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -762,36 +2859,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1112,26 +3218,30 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
+      <c r="G2" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="3" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
@@ -1141,7 +3251,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
+      <c r="H3" s="13"/>
     </row>
     <row r="4" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
@@ -1151,7 +3261,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
+      <c r="H4" s="13"/>
     </row>
     <row r="5" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
@@ -1161,29 +3271,33 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="11"/>
-      <c r="H5" s="11"/>
+      <c r="H5" s="14"/>
     </row>
     <row r="6" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
+      <c r="G6" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="7" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
@@ -1193,7 +3307,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
+      <c r="H7" s="13"/>
     </row>
     <row r="8" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
@@ -1203,7 +3317,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
+      <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
@@ -1213,29 +3327,33 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
+      <c r="H9" s="14"/>
     </row>
     <row r="10" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
+      <c r="G10" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>240</v>
+      </c>
     </row>
     <row r="11" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
@@ -1245,7 +3363,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
+      <c r="H11" s="13"/>
     </row>
     <row r="12" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
@@ -1255,7 +3373,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
+      <c r="H12" s="13"/>
     </row>
     <row r="13" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
@@ -1265,29 +3383,33 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
+      <c r="H13" s="14"/>
     </row>
     <row r="14" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="7" t="s">
+      <c r="F14" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
+      <c r="G14" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="15" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
@@ -1297,7 +3419,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
+      <c r="H15" s="13"/>
     </row>
     <row r="16" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
@@ -1307,7 +3429,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
+      <c r="H16" s="13"/>
     </row>
     <row r="17" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
@@ -1317,29 +3439,33 @@
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
+      <c r="H17" s="14"/>
     </row>
     <row r="18" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="7" t="s">
+      <c r="F18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
+      <c r="G18" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H18" s="12" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="19" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
@@ -1349,7 +3475,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
+      <c r="H19" s="13"/>
     </row>
     <row r="20" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
@@ -1359,7 +3485,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
       <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
+      <c r="H20" s="13"/>
     </row>
     <row r="21" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
@@ -1369,29 +3495,33 @@
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
+      <c r="H21" s="14"/>
     </row>
     <row r="22" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="E22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="F22" s="7" t="s">
+      <c r="F22" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
+      <c r="G22" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="23" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
@@ -1401,7 +3531,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
+      <c r="H23" s="13"/>
     </row>
     <row r="24" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
@@ -1411,7 +3541,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
       <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
+      <c r="H24" s="13"/>
     </row>
     <row r="25" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
@@ -1421,29 +3551,33 @@
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
+      <c r="H25" s="14"/>
     </row>
     <row r="26" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="F26" s="7" t="s">
+      <c r="F26" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
+      <c r="G26" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H26" s="12" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="27" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
@@ -1453,7 +3587,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
       <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
+      <c r="H27" s="13"/>
     </row>
     <row r="28" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
@@ -1463,7 +3597,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
       <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
+      <c r="H28" s="13"/>
     </row>
     <row r="29" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
@@ -1473,29 +3607,33 @@
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
+      <c r="H29" s="14"/>
     </row>
     <row r="30" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
+      <c r="G30" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="31" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
@@ -1505,7 +3643,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
       <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
+      <c r="H31" s="13"/>
     </row>
     <row r="32" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
@@ -1515,7 +3653,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
       <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
+      <c r="H32" s="13"/>
     </row>
     <row r="33" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
@@ -1525,29 +3663,33 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
+      <c r="H33" s="14"/>
     </row>
     <row r="34" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="B34" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E34" s="8" t="s">
+      <c r="E34" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
+      <c r="G34" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="H34" s="12" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="35" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
@@ -1557,7 +3699,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
+      <c r="H35" s="13"/>
     </row>
     <row r="36" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
@@ -1567,7 +3709,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
+      <c r="H36" s="13"/>
     </row>
     <row r="37" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4"/>
@@ -1577,29 +3719,33 @@
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
+      <c r="H37" s="14"/>
     </row>
     <row r="38" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="B38" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="C38" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E38" s="8" t="s">
+      <c r="E38" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G38" s="9"/>
-      <c r="H38" s="9"/>
+      <c r="G38" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="39" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
@@ -1609,7 +3755,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
       <c r="G39" s="10"/>
-      <c r="H39" s="10"/>
+      <c r="H39" s="13"/>
     </row>
     <row r="40" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
@@ -1619,7 +3765,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
       <c r="G40" s="10"/>
-      <c r="H40" s="10"/>
+      <c r="H40" s="13"/>
     </row>
     <row r="41" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4"/>
@@ -1629,29 +3775,33 @@
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="11"/>
-      <c r="H41" s="11"/>
+      <c r="H41" s="14"/>
     </row>
     <row r="42" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C42" s="2" t="s">
+      <c r="C42" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="E42" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="F42" s="7" t="s">
+      <c r="F42" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G42" s="9"/>
-      <c r="H42" s="9"/>
+      <c r="G42" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H42" s="12" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="43" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
@@ -1661,7 +3811,7 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
       <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
+      <c r="H43" s="13"/>
     </row>
     <row r="44" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
@@ -1671,7 +3821,7 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
       <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
+      <c r="H44" s="13"/>
     </row>
     <row r="45" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4"/>
@@ -1681,29 +3831,33 @@
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
+      <c r="H45" s="14"/>
     </row>
     <row r="46" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B46" s="7" t="s">
+      <c r="B46" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="E46" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="7" t="s">
+      <c r="F46" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G46" s="9"/>
-      <c r="H46" s="9"/>
+      <c r="G46" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="H46" s="12" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="47" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
@@ -1713,7 +3867,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
       <c r="G47" s="10"/>
-      <c r="H47" s="10"/>
+      <c r="H47" s="13"/>
     </row>
     <row r="48" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
@@ -1723,7 +3877,7 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
       <c r="G48" s="10"/>
-      <c r="H48" s="10"/>
+      <c r="H48" s="13"/>
     </row>
     <row r="49" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
@@ -1733,29 +3887,33 @@
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="11"/>
-      <c r="H49" s="11"/>
+      <c r="H49" s="14"/>
     </row>
     <row r="50" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="E50" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="F50" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
+      <c r="G50" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="H50" s="12" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="51" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
@@ -1765,7 +3923,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
       <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
+      <c r="H51" s="13"/>
     </row>
     <row r="52" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
@@ -1775,7 +3933,7 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
       <c r="G52" s="10"/>
-      <c r="H52" s="10"/>
+      <c r="H52" s="13"/>
     </row>
     <row r="53" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4"/>
@@ -1785,29 +3943,33 @@
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="11"/>
-      <c r="H53" s="11"/>
+      <c r="H53" s="14"/>
     </row>
     <row r="54" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B54" s="7" t="s">
+      <c r="B54" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C54" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E54" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F54" s="7" t="s">
+      <c r="F54" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G54" s="9"/>
-      <c r="H54" s="9"/>
+      <c r="G54" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H54" s="12" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="55" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
@@ -1817,7 +3979,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
       <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
+      <c r="H55" s="13"/>
     </row>
     <row r="56" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
@@ -1827,7 +3989,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
       <c r="G56" s="10"/>
-      <c r="H56" s="10"/>
+      <c r="H56" s="13"/>
     </row>
     <row r="57" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4"/>
@@ -1837,29 +3999,33 @@
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="11"/>
-      <c r="H57" s="11"/>
+      <c r="H57" s="14"/>
     </row>
     <row r="58" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C58" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D58" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="E58" s="8" t="s">
+      <c r="E58" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="F58" s="7" t="s">
+      <c r="F58" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G58" s="9"/>
-      <c r="H58" s="9"/>
+      <c r="G58" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="H58" s="12" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="59" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
@@ -1869,7 +4035,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
       <c r="G59" s="10"/>
-      <c r="H59" s="10"/>
+      <c r="H59" s="13"/>
     </row>
     <row r="60" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
@@ -1879,7 +4045,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
       <c r="G60" s="10"/>
-      <c r="H60" s="10"/>
+      <c r="H60" s="13"/>
     </row>
     <row r="61" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4"/>
@@ -1889,29 +4055,33 @@
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
       <c r="G61" s="11"/>
-      <c r="H61" s="11"/>
+      <c r="H61" s="14"/>
     </row>
     <row r="62" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B62" s="7" t="s">
+      <c r="B62" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D62" s="6" t="s">
+      <c r="D62" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="E62" s="8" t="s">
+      <c r="E62" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="F62" s="7" t="s">
+      <c r="F62" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G62" s="9"/>
-      <c r="H62" s="9"/>
+      <c r="G62" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="H62" s="12" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="63" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
@@ -1921,7 +4091,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
       <c r="G63" s="10"/>
-      <c r="H63" s="10"/>
+      <c r="H63" s="13"/>
     </row>
     <row r="64" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
@@ -1931,7 +4101,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
       <c r="G64" s="10"/>
-      <c r="H64" s="10"/>
+      <c r="H64" s="13"/>
     </row>
     <row r="65" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4"/>
@@ -1941,29 +4111,33 @@
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="11"/>
-      <c r="H65" s="11"/>
+      <c r="H65" s="14"/>
     </row>
     <row r="66" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B66" s="7" t="s">
+      <c r="B66" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C66" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D66" s="6" t="s">
+      <c r="D66" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E66" s="8" t="s">
+      <c r="E66" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="F66" s="7" t="s">
+      <c r="F66" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G66" s="9"/>
-      <c r="H66" s="9"/>
+      <c r="G66" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H66" s="12" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="67" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3"/>
@@ -1973,7 +4147,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
       <c r="G67" s="10"/>
-      <c r="H67" s="10"/>
+      <c r="H67" s="13"/>
     </row>
     <row r="68" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
@@ -1983,7 +4157,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
       <c r="G68" s="10"/>
-      <c r="H68" s="10"/>
+      <c r="H68" s="13"/>
     </row>
     <row r="69" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4"/>
@@ -1993,29 +4167,33 @@
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="G69" s="11"/>
-      <c r="H69" s="11"/>
+      <c r="H69" s="14"/>
     </row>
     <row r="70" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B70" s="7" t="s">
+      <c r="B70" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="C70" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D70" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="E70" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="F70" s="7" t="s">
+      <c r="F70" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G70" s="9"/>
-      <c r="H70" s="9"/>
+      <c r="G70" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="H70" s="12" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="71" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
@@ -2025,7 +4203,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
       <c r="G71" s="10"/>
-      <c r="H71" s="10"/>
+      <c r="H71" s="13"/>
     </row>
     <row r="72" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
@@ -2035,7 +4213,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
       <c r="G72" s="10"/>
-      <c r="H72" s="10"/>
+      <c r="H72" s="13"/>
     </row>
     <row r="73" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4"/>
@@ -2045,29 +4223,33 @@
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
       <c r="G73" s="11"/>
-      <c r="H73" s="11"/>
+      <c r="H73" s="14"/>
     </row>
     <row r="74" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="B74" s="7" t="s">
+      <c r="B74" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C74" s="2" t="s">
+      <c r="C74" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D74" s="6" t="s">
+      <c r="D74" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E74" s="8" t="s">
+      <c r="E74" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="F74" s="7" t="s">
+      <c r="F74" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G74" s="9"/>
-      <c r="H74" s="9"/>
+      <c r="G74" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H74" s="12" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="75" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3"/>
@@ -2077,7 +4259,7 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
       <c r="G75" s="10"/>
-      <c r="H75" s="10"/>
+      <c r="H75" s="13"/>
     </row>
     <row r="76" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
@@ -2087,7 +4269,7 @@
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
       <c r="G76" s="10"/>
-      <c r="H76" s="10"/>
+      <c r="H76" s="13"/>
     </row>
     <row r="77" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4"/>
@@ -2097,29 +4279,33 @@
       <c r="E77" s="4"/>
       <c r="F77" s="4"/>
       <c r="G77" s="11"/>
-      <c r="H77" s="11"/>
+      <c r="H77" s="14"/>
     </row>
     <row r="78" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="5" t="s">
+      <c r="A78" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="B78" s="7" t="s">
+      <c r="B78" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D78" s="6" t="s">
+      <c r="D78" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E78" s="8" t="s">
+      <c r="E78" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F78" s="7" t="s">
+      <c r="F78" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G78" s="9"/>
-      <c r="H78" s="9"/>
+      <c r="G78" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="H78" s="12" t="s">
+        <v>276</v>
+      </c>
     </row>
     <row r="79" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3"/>
@@ -2129,7 +4315,7 @@
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
       <c r="G79" s="10"/>
-      <c r="H79" s="10"/>
+      <c r="H79" s="13"/>
     </row>
     <row r="80" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
@@ -2139,7 +4325,7 @@
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="10"/>
-      <c r="H80" s="10"/>
+      <c r="H80" s="13"/>
     </row>
     <row r="81" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4"/>
@@ -2149,29 +4335,33 @@
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
       <c r="G81" s="11"/>
-      <c r="H81" s="11"/>
+      <c r="H81" s="14"/>
     </row>
     <row r="82" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="5" t="s">
+      <c r="A82" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B82" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C82" s="2" t="s">
+      <c r="C82" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D82" s="6" t="s">
+      <c r="D82" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E82" s="8" t="s">
+      <c r="E82" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="F82" s="7" t="s">
+      <c r="F82" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G82" s="9"/>
-      <c r="H82" s="9"/>
+      <c r="G82" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H82" s="12" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="83" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
@@ -2181,7 +4371,7 @@
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
       <c r="G83" s="10"/>
-      <c r="H83" s="10"/>
+      <c r="H83" s="13"/>
     </row>
     <row r="84" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3"/>
@@ -2191,7 +4381,7 @@
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
       <c r="G84" s="10"/>
-      <c r="H84" s="10"/>
+      <c r="H84" s="13"/>
     </row>
     <row r="85" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4"/>
@@ -2201,29 +4391,33 @@
       <c r="E85" s="4"/>
       <c r="F85" s="4"/>
       <c r="G85" s="11"/>
-      <c r="H85" s="11"/>
+      <c r="H85" s="14"/>
     </row>
     <row r="86" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="5" t="s">
+      <c r="A86" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B86" s="7" t="s">
+      <c r="B86" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C86" s="2" t="s">
+      <c r="C86" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D86" s="6" t="s">
+      <c r="D86" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E86" s="8" t="s">
+      <c r="E86" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="F86" s="7" t="s">
+      <c r="F86" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G86" s="9"/>
-      <c r="H86" s="9"/>
+      <c r="G86" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H86" s="12" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="87" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
@@ -2233,7 +4427,7 @@
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="10"/>
-      <c r="H87" s="10"/>
+      <c r="H87" s="13"/>
     </row>
     <row r="88" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
@@ -2243,7 +4437,7 @@
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="10"/>
+      <c r="H88" s="13"/>
     </row>
     <row r="89" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="4"/>
@@ -2253,29 +4447,33 @@
       <c r="E89" s="4"/>
       <c r="F89" s="4"/>
       <c r="G89" s="11"/>
-      <c r="H89" s="11"/>
+      <c r="H89" s="14"/>
     </row>
     <row r="90" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="5" t="s">
+      <c r="A90" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B90" s="7" t="s">
+      <c r="B90" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C90" s="2" t="s">
+      <c r="C90" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="D90" s="6" t="s">
+      <c r="D90" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E90" s="8" t="s">
+      <c r="E90" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="F90" s="7" t="s">
+      <c r="F90" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G90" s="9"/>
-      <c r="H90" s="9"/>
+      <c r="G90" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H90" s="12" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="91" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
@@ -2285,7 +4483,7 @@
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
       <c r="G91" s="10"/>
-      <c r="H91" s="10"/>
+      <c r="H91" s="13"/>
     </row>
     <row r="92" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
@@ -2295,7 +4493,7 @@
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
       <c r="G92" s="10"/>
-      <c r="H92" s="10"/>
+      <c r="H92" s="13"/>
     </row>
     <row r="93" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="4"/>
@@ -2305,29 +4503,33 @@
       <c r="E93" s="4"/>
       <c r="F93" s="4"/>
       <c r="G93" s="11"/>
-      <c r="H93" s="11"/>
+      <c r="H93" s="14"/>
     </row>
     <row r="94" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="5" t="s">
+      <c r="A94" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="B94" s="7" t="s">
+      <c r="B94" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C94" s="2" t="s">
+      <c r="C94" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="D94" s="6" t="s">
+      <c r="D94" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E94" s="8" t="s">
+      <c r="E94" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="F94" s="7" t="s">
+      <c r="F94" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G94" s="9"/>
-      <c r="H94" s="9"/>
+      <c r="G94" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="H94" s="12" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="95" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
@@ -2337,7 +4539,7 @@
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
       <c r="G95" s="10"/>
-      <c r="H95" s="10"/>
+      <c r="H95" s="13"/>
     </row>
     <row r="96" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
@@ -2347,7 +4549,7 @@
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
       <c r="G96" s="10"/>
-      <c r="H96" s="10"/>
+      <c r="H96" s="13"/>
     </row>
     <row r="97" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="4"/>
@@ -2357,29 +4559,33 @@
       <c r="E97" s="4"/>
       <c r="F97" s="4"/>
       <c r="G97" s="11"/>
-      <c r="H97" s="11"/>
+      <c r="H97" s="14"/>
     </row>
     <row r="98" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="5" t="s">
+      <c r="A98" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B98" s="7" t="s">
+      <c r="B98" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C98" s="2" t="s">
+      <c r="C98" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="D98" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E98" s="8" t="s">
+      <c r="E98" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="F98" s="7" t="s">
+      <c r="F98" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G98" s="9"/>
-      <c r="H98" s="9"/>
+      <c r="G98" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="H98" s="12" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="99" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
@@ -2389,7 +4595,7 @@
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
       <c r="G99" s="10"/>
-      <c r="H99" s="10"/>
+      <c r="H99" s="13"/>
     </row>
     <row r="100" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
@@ -2399,7 +4605,7 @@
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="10"/>
-      <c r="H100" s="10"/>
+      <c r="H100" s="13"/>
     </row>
     <row r="101" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="4"/>
@@ -2409,29 +4615,33 @@
       <c r="E101" s="4"/>
       <c r="F101" s="4"/>
       <c r="G101" s="11"/>
-      <c r="H101" s="11"/>
+      <c r="H101" s="14"/>
     </row>
     <row r="102" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="5" t="s">
+      <c r="A102" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B102" s="7" t="s">
+      <c r="B102" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C102" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="D102" s="6" t="s">
+      <c r="D102" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E102" s="8" t="s">
+      <c r="E102" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="F102" s="7" t="s">
+      <c r="F102" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G102" s="9"/>
-      <c r="H102" s="9"/>
+      <c r="G102" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="H102" s="12" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="103" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="3"/>
@@ -2441,7 +4651,7 @@
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
       <c r="G103" s="10"/>
-      <c r="H103" s="10"/>
+      <c r="H103" s="13"/>
     </row>
     <row r="104" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="3"/>
@@ -2451,7 +4661,7 @@
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
       <c r="G104" s="10"/>
-      <c r="H104" s="10"/>
+      <c r="H104" s="13"/>
     </row>
     <row r="105" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="4"/>
@@ -2461,29 +4671,33 @@
       <c r="E105" s="4"/>
       <c r="F105" s="4"/>
       <c r="G105" s="11"/>
-      <c r="H105" s="11"/>
+      <c r="H105" s="14"/>
     </row>
     <row r="106" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="5" t="s">
+      <c r="A106" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B106" s="7" t="s">
+      <c r="B106" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C106" s="2" t="s">
+      <c r="C106" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="D106" s="6" t="s">
+      <c r="D106" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E106" s="8" t="s">
+      <c r="E106" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="F106" s="7" t="s">
+      <c r="F106" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G106" s="9"/>
-      <c r="H106" s="9"/>
+      <c r="G106" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H106" s="12" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="107" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="3"/>
@@ -2493,7 +4707,7 @@
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
       <c r="G107" s="10"/>
-      <c r="H107" s="10"/>
+      <c r="H107" s="13"/>
     </row>
     <row r="108" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="3"/>
@@ -2503,7 +4717,7 @@
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
       <c r="G108" s="10"/>
-      <c r="H108" s="10"/>
+      <c r="H108" s="13"/>
     </row>
     <row r="109" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="4"/>
@@ -2513,29 +4727,33 @@
       <c r="E109" s="4"/>
       <c r="F109" s="4"/>
       <c r="G109" s="11"/>
-      <c r="H109" s="11"/>
+      <c r="H109" s="14"/>
     </row>
     <row r="110" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="5" t="s">
+      <c r="A110" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B110" s="7" t="s">
+      <c r="B110" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C110" s="2" t="s">
+      <c r="C110" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D110" s="6" t="s">
+      <c r="D110" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E110" s="8" t="s">
+      <c r="E110" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="F110" s="7" t="s">
+      <c r="F110" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G110" s="9"/>
-      <c r="H110" s="9"/>
+      <c r="G110" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="H110" s="12" t="s">
+        <v>275</v>
+      </c>
     </row>
     <row r="111" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="3"/>
@@ -2545,7 +4763,7 @@
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
       <c r="G111" s="10"/>
-      <c r="H111" s="10"/>
+      <c r="H111" s="13"/>
     </row>
     <row r="112" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="3"/>
@@ -2555,7 +4773,7 @@
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
       <c r="G112" s="10"/>
-      <c r="H112" s="10"/>
+      <c r="H112" s="13"/>
     </row>
     <row r="113" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="4"/>
@@ -2565,29 +4783,33 @@
       <c r="E113" s="4"/>
       <c r="F113" s="4"/>
       <c r="G113" s="11"/>
-      <c r="H113" s="11"/>
+      <c r="H113" s="14"/>
     </row>
     <row r="114" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="5" t="s">
+      <c r="A114" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B114" s="7" t="s">
+      <c r="B114" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C114" s="2" t="s">
+      <c r="C114" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="D114" s="6" t="s">
+      <c r="D114" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E114" s="8" t="s">
+      <c r="E114" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="F114" s="7" t="s">
+      <c r="F114" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G114" s="9"/>
-      <c r="H114" s="9"/>
+      <c r="G114" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="H114" s="12" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="115" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="3"/>
@@ -2597,7 +4819,7 @@
       <c r="E115" s="3"/>
       <c r="F115" s="3"/>
       <c r="G115" s="10"/>
-      <c r="H115" s="10"/>
+      <c r="H115" s="13"/>
     </row>
     <row r="116" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="3"/>
@@ -2607,7 +4829,7 @@
       <c r="E116" s="3"/>
       <c r="F116" s="3"/>
       <c r="G116" s="10"/>
-      <c r="H116" s="10"/>
+      <c r="H116" s="13"/>
     </row>
     <row r="117" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="4"/>
@@ -2617,29 +4839,33 @@
       <c r="E117" s="4"/>
       <c r="F117" s="4"/>
       <c r="G117" s="11"/>
-      <c r="H117" s="11"/>
+      <c r="H117" s="14"/>
     </row>
     <row r="118" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="5" t="s">
+      <c r="A118" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B118" s="7" t="s">
+      <c r="B118" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="D118" s="6" t="s">
+      <c r="D118" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E118" s="8" t="s">
+      <c r="E118" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="F118" s="7" t="s">
+      <c r="F118" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G118" s="9"/>
-      <c r="H118" s="9"/>
+      <c r="G118" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="H118" s="12" t="s">
+        <v>274</v>
+      </c>
     </row>
     <row r="119" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="3"/>
@@ -2649,7 +4875,7 @@
       <c r="E119" s="3"/>
       <c r="F119" s="3"/>
       <c r="G119" s="10"/>
-      <c r="H119" s="10"/>
+      <c r="H119" s="13"/>
     </row>
     <row r="120" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="3"/>
@@ -2659,7 +4885,7 @@
       <c r="E120" s="3"/>
       <c r="F120" s="3"/>
       <c r="G120" s="10"/>
-      <c r="H120" s="10"/>
+      <c r="H120" s="13"/>
     </row>
     <row r="121" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="4"/>
@@ -2669,29 +4895,33 @@
       <c r="E121" s="4"/>
       <c r="F121" s="4"/>
       <c r="G121" s="11"/>
-      <c r="H121" s="11"/>
+      <c r="H121" s="14"/>
     </row>
     <row r="122" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="5" t="s">
+      <c r="A122" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B122" s="7" t="s">
+      <c r="B122" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C122" s="2" t="s">
+      <c r="C122" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="D122" s="6" t="s">
+      <c r="D122" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E122" s="8" t="s">
+      <c r="E122" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="F122" s="7" t="s">
+      <c r="F122" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G122" s="9"/>
-      <c r="H122" s="9"/>
+      <c r="G122" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="H122" s="12" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="123" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="3"/>
@@ -2701,7 +4931,7 @@
       <c r="E123" s="3"/>
       <c r="F123" s="3"/>
       <c r="G123" s="10"/>
-      <c r="H123" s="10"/>
+      <c r="H123" s="13"/>
     </row>
     <row r="124" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="3"/>
@@ -2711,7 +4941,7 @@
       <c r="E124" s="3"/>
       <c r="F124" s="3"/>
       <c r="G124" s="10"/>
-      <c r="H124" s="10"/>
+      <c r="H124" s="13"/>
     </row>
     <row r="125" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="4"/>
@@ -2721,29 +4951,33 @@
       <c r="E125" s="4"/>
       <c r="F125" s="4"/>
       <c r="G125" s="11"/>
-      <c r="H125" s="11"/>
+      <c r="H125" s="14"/>
     </row>
     <row r="126" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="5" t="s">
+      <c r="A126" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B126" s="7" t="s">
+      <c r="B126" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C126" s="2" t="s">
+      <c r="C126" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="D126" s="6" t="s">
+      <c r="D126" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="E126" s="8" t="s">
+      <c r="E126" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="F126" s="7" t="s">
+      <c r="F126" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G126" s="9"/>
-      <c r="H126" s="9"/>
+      <c r="G126" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="H126" s="12" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="127" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="3"/>
@@ -2753,7 +4987,7 @@
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
       <c r="G127" s="10"/>
-      <c r="H127" s="10"/>
+      <c r="H127" s="13"/>
     </row>
     <row r="128" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="3"/>
@@ -2763,7 +4997,7 @@
       <c r="E128" s="3"/>
       <c r="F128" s="3"/>
       <c r="G128" s="10"/>
-      <c r="H128" s="10"/>
+      <c r="H128" s="13"/>
     </row>
     <row r="129" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="4"/>
@@ -2773,29 +5007,33 @@
       <c r="E129" s="4"/>
       <c r="F129" s="4"/>
       <c r="G129" s="11"/>
-      <c r="H129" s="11"/>
+      <c r="H129" s="14"/>
     </row>
     <row r="130" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="5" t="s">
+      <c r="A130" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="B130" s="7" t="s">
+      <c r="B130" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C130" s="2" t="s">
+      <c r="C130" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D130" s="6" t="s">
+      <c r="D130" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="E130" s="8" t="s">
+      <c r="E130" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="F130" s="7" t="s">
+      <c r="F130" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G130" s="9"/>
-      <c r="H130" s="9"/>
+      <c r="G130" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="H130" s="12" t="s">
+        <v>258</v>
+      </c>
     </row>
     <row r="131" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="3"/>
@@ -2805,7 +5043,7 @@
       <c r="E131" s="3"/>
       <c r="F131" s="3"/>
       <c r="G131" s="10"/>
-      <c r="H131" s="10"/>
+      <c r="H131" s="13"/>
     </row>
     <row r="132" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="3"/>
@@ -2815,7 +5053,7 @@
       <c r="E132" s="3"/>
       <c r="F132" s="3"/>
       <c r="G132" s="10"/>
-      <c r="H132" s="10"/>
+      <c r="H132" s="13"/>
     </row>
     <row r="133" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="4"/>
@@ -2825,29 +5063,33 @@
       <c r="E133" s="4"/>
       <c r="F133" s="4"/>
       <c r="G133" s="11"/>
-      <c r="H133" s="11"/>
+      <c r="H133" s="14"/>
     </row>
     <row r="134" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="5" t="s">
+      <c r="A134" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="B134" s="7" t="s">
+      <c r="B134" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="C134" s="2" t="s">
+      <c r="C134" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="D134" s="6" t="s">
+      <c r="D134" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E134" s="8" t="s">
+      <c r="E134" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="F134" s="7" t="s">
+      <c r="F134" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G134" s="9"/>
-      <c r="H134" s="9"/>
+      <c r="G134" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="H134" s="12" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="135" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="3"/>
@@ -2857,7 +5099,7 @@
       <c r="E135" s="3"/>
       <c r="F135" s="3"/>
       <c r="G135" s="10"/>
-      <c r="H135" s="10"/>
+      <c r="H135" s="13"/>
     </row>
     <row r="136" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="3"/>
@@ -2867,7 +5109,7 @@
       <c r="E136" s="3"/>
       <c r="F136" s="3"/>
       <c r="G136" s="10"/>
-      <c r="H136" s="10"/>
+      <c r="H136" s="13"/>
     </row>
     <row r="137" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="4"/>
@@ -2877,29 +5119,33 @@
       <c r="E137" s="4"/>
       <c r="F137" s="4"/>
       <c r="G137" s="11"/>
-      <c r="H137" s="11"/>
+      <c r="H137" s="14"/>
     </row>
     <row r="138" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="5" t="s">
+      <c r="A138" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="B138" s="7" t="s">
+      <c r="B138" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C138" s="2" t="s">
+      <c r="C138" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="D138" s="6" t="s">
+      <c r="D138" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E138" s="8" t="s">
+      <c r="E138" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="F138" s="7" t="s">
+      <c r="F138" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G138" s="9"/>
-      <c r="H138" s="9"/>
+      <c r="G138" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="H138" s="12" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="139" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="3"/>
@@ -2909,7 +5155,7 @@
       <c r="E139" s="3"/>
       <c r="F139" s="3"/>
       <c r="G139" s="10"/>
-      <c r="H139" s="10"/>
+      <c r="H139" s="13"/>
     </row>
     <row r="140" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="3"/>
@@ -2919,7 +5165,7 @@
       <c r="E140" s="3"/>
       <c r="F140" s="3"/>
       <c r="G140" s="10"/>
-      <c r="H140" s="10"/>
+      <c r="H140" s="13"/>
     </row>
     <row r="141" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="4"/>
@@ -2929,29 +5175,33 @@
       <c r="E141" s="4"/>
       <c r="F141" s="4"/>
       <c r="G141" s="11"/>
-      <c r="H141" s="11"/>
+      <c r="H141" s="14"/>
     </row>
     <row r="142" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="5" t="s">
+      <c r="A142" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B142" s="7" t="s">
+      <c r="B142" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C142" s="2" t="s">
+      <c r="C142" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="D142" s="6" t="s">
+      <c r="D142" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E142" s="8" t="s">
+      <c r="E142" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="F142" s="7" t="s">
+      <c r="F142" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G142" s="9"/>
-      <c r="H142" s="9"/>
+      <c r="G142" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="H142" s="12" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="143" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="3"/>
@@ -2961,7 +5211,7 @@
       <c r="E143" s="3"/>
       <c r="F143" s="3"/>
       <c r="G143" s="10"/>
-      <c r="H143" s="10"/>
+      <c r="H143" s="13"/>
     </row>
     <row r="144" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="3"/>
@@ -2971,7 +5221,7 @@
       <c r="E144" s="3"/>
       <c r="F144" s="3"/>
       <c r="G144" s="10"/>
-      <c r="H144" s="10"/>
+      <c r="H144" s="13"/>
     </row>
     <row r="145" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="4"/>
@@ -2981,29 +5231,33 @@
       <c r="E145" s="4"/>
       <c r="F145" s="4"/>
       <c r="G145" s="11"/>
-      <c r="H145" s="11"/>
+      <c r="H145" s="14"/>
     </row>
     <row r="146" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="5" t="s">
+      <c r="A146" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="B146" s="7" t="s">
+      <c r="B146" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="C146" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="D146" s="6" t="s">
+      <c r="D146" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E146" s="8" t="s">
+      <c r="E146" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="F146" s="7" t="s">
+      <c r="F146" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G146" s="9"/>
-      <c r="H146" s="9"/>
+      <c r="G146" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="H146" s="12" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="147" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="3"/>
@@ -3013,7 +5267,7 @@
       <c r="E147" s="3"/>
       <c r="F147" s="3"/>
       <c r="G147" s="10"/>
-      <c r="H147" s="10"/>
+      <c r="H147" s="13"/>
     </row>
     <row r="148" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="3"/>
@@ -3023,7 +5277,7 @@
       <c r="E148" s="3"/>
       <c r="F148" s="3"/>
       <c r="G148" s="10"/>
-      <c r="H148" s="10"/>
+      <c r="H148" s="13"/>
     </row>
     <row r="149" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="4"/>
@@ -3033,29 +5287,33 @@
       <c r="E149" s="4"/>
       <c r="F149" s="4"/>
       <c r="G149" s="11"/>
-      <c r="H149" s="11"/>
+      <c r="H149" s="14"/>
     </row>
     <row r="150" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="5" t="s">
+      <c r="A150" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="B150" s="7" t="s">
+      <c r="B150" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C150" s="2" t="s">
+      <c r="C150" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="D150" s="6" t="s">
+      <c r="D150" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E150" s="8" t="s">
+      <c r="E150" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="F150" s="7" t="s">
+      <c r="F150" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G150" s="9"/>
-      <c r="H150" s="9"/>
+      <c r="G150" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="H150" s="12" t="s">
+        <v>261</v>
+      </c>
     </row>
     <row r="151" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="3"/>
@@ -3065,7 +5323,7 @@
       <c r="E151" s="3"/>
       <c r="F151" s="3"/>
       <c r="G151" s="10"/>
-      <c r="H151" s="10"/>
+      <c r="H151" s="13"/>
     </row>
     <row r="152" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="3"/>
@@ -3075,7 +5333,7 @@
       <c r="E152" s="3"/>
       <c r="F152" s="3"/>
       <c r="G152" s="10"/>
-      <c r="H152" s="10"/>
+      <c r="H152" s="13"/>
     </row>
     <row r="153" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="4"/>
@@ -3085,27 +5343,31 @@
       <c r="E153" s="4"/>
       <c r="F153" s="4"/>
       <c r="G153" s="11"/>
-      <c r="H153" s="11"/>
+      <c r="H153" s="14"/>
     </row>
     <row r="154" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="5" t="s">
+      <c r="A154" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="B154" s="7"/>
-      <c r="C154" s="2" t="s">
+      <c r="B154" s="5"/>
+      <c r="C154" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="D154" s="6" t="s">
+      <c r="D154" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E154" s="8" t="s">
+      <c r="E154" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="F154" s="7" t="s">
+      <c r="F154" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G154" s="9"/>
-      <c r="H154" s="9"/>
+      <c r="G154" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="H154" s="12" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="155" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="3"/>
@@ -3115,7 +5377,7 @@
       <c r="E155" s="3"/>
       <c r="F155" s="3"/>
       <c r="G155" s="10"/>
-      <c r="H155" s="10"/>
+      <c r="H155" s="13"/>
     </row>
     <row r="156" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="3"/>
@@ -3125,7 +5387,7 @@
       <c r="E156" s="3"/>
       <c r="F156" s="3"/>
       <c r="G156" s="10"/>
-      <c r="H156" s="10"/>
+      <c r="H156" s="13"/>
     </row>
     <row r="157" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="4"/>
@@ -3135,29 +5397,33 @@
       <c r="E157" s="4"/>
       <c r="F157" s="4"/>
       <c r="G157" s="11"/>
-      <c r="H157" s="11"/>
+      <c r="H157" s="14"/>
     </row>
     <row r="158" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="5" t="s">
+      <c r="A158" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="B158" s="7" t="s">
+      <c r="B158" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C158" s="2" t="s">
+      <c r="C158" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D158" s="6" t="s">
+      <c r="D158" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E158" s="8" t="s">
+      <c r="E158" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="F158" s="7" t="s">
+      <c r="F158" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G158" s="9"/>
-      <c r="H158" s="9"/>
+      <c r="G158" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="H158" s="12" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="159" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="3"/>
@@ -3167,7 +5433,7 @@
       <c r="E159" s="3"/>
       <c r="F159" s="3"/>
       <c r="G159" s="10"/>
-      <c r="H159" s="10"/>
+      <c r="H159" s="13"/>
     </row>
     <row r="160" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="3"/>
@@ -3177,7 +5443,7 @@
       <c r="E160" s="3"/>
       <c r="F160" s="3"/>
       <c r="G160" s="10"/>
-      <c r="H160" s="10"/>
+      <c r="H160" s="13"/>
     </row>
     <row r="161" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="4"/>
@@ -3187,29 +5453,33 @@
       <c r="E161" s="4"/>
       <c r="F161" s="4"/>
       <c r="G161" s="11"/>
-      <c r="H161" s="11"/>
+      <c r="H161" s="14"/>
     </row>
     <row r="162" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="5" t="s">
+      <c r="A162" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B162" s="7" t="s">
+      <c r="B162" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C162" s="2" t="s">
+      <c r="C162" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="D162" s="6" t="s">
+      <c r="D162" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E162" s="8" t="s">
+      <c r="E162" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="F162" s="7" t="s">
+      <c r="F162" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G162" s="9"/>
-      <c r="H162" s="9"/>
+      <c r="G162" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="H162" s="12" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="163" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="3"/>
@@ -3219,7 +5489,7 @@
       <c r="E163" s="3"/>
       <c r="F163" s="3"/>
       <c r="G163" s="10"/>
-      <c r="H163" s="10"/>
+      <c r="H163" s="13"/>
     </row>
     <row r="164" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="3"/>
@@ -3229,7 +5499,7 @@
       <c r="E164" s="3"/>
       <c r="F164" s="3"/>
       <c r="G164" s="10"/>
-      <c r="H164" s="10"/>
+      <c r="H164" s="13"/>
     </row>
     <row r="165" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="4"/>
@@ -3239,29 +5509,33 @@
       <c r="E165" s="4"/>
       <c r="F165" s="4"/>
       <c r="G165" s="11"/>
-      <c r="H165" s="11"/>
+      <c r="H165" s="14"/>
     </row>
     <row r="166" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="5" t="s">
+      <c r="A166" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B166" s="7" t="s">
+      <c r="B166" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C166" s="2" t="s">
+      <c r="C166" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="D166" s="6" t="s">
+      <c r="D166" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E166" s="8" t="s">
+      <c r="E166" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="F166" s="7" t="s">
+      <c r="F166" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G166" s="9"/>
-      <c r="H166" s="9"/>
+      <c r="G166" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="H166" s="12" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="167" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="3"/>
@@ -3271,7 +5545,7 @@
       <c r="E167" s="3"/>
       <c r="F167" s="3"/>
       <c r="G167" s="10"/>
-      <c r="H167" s="10"/>
+      <c r="H167" s="13"/>
     </row>
     <row r="168" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="3"/>
@@ -3281,7 +5555,7 @@
       <c r="E168" s="3"/>
       <c r="F168" s="3"/>
       <c r="G168" s="10"/>
-      <c r="H168" s="10"/>
+      <c r="H168" s="13"/>
     </row>
     <row r="169" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="4"/>
@@ -3291,29 +5565,33 @@
       <c r="E169" s="4"/>
       <c r="F169" s="4"/>
       <c r="G169" s="11"/>
-      <c r="H169" s="11"/>
+      <c r="H169" s="14"/>
     </row>
     <row r="170" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="5" t="s">
+      <c r="A170" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="B170" s="7" t="s">
+      <c r="B170" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C170" s="2" t="s">
+      <c r="C170" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="D170" s="6" t="s">
+      <c r="D170" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E170" s="8" t="s">
+      <c r="E170" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="F170" s="7" t="s">
+      <c r="F170" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G170" s="9"/>
-      <c r="H170" s="9"/>
+      <c r="G170" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="H170" s="12" t="s">
+        <v>270</v>
+      </c>
     </row>
     <row r="171" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="3"/>
@@ -3323,7 +5601,7 @@
       <c r="E171" s="3"/>
       <c r="F171" s="3"/>
       <c r="G171" s="10"/>
-      <c r="H171" s="10"/>
+      <c r="H171" s="13"/>
     </row>
     <row r="172" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="3"/>
@@ -3333,7 +5611,7 @@
       <c r="E172" s="3"/>
       <c r="F172" s="3"/>
       <c r="G172" s="10"/>
-      <c r="H172" s="10"/>
+      <c r="H172" s="13"/>
     </row>
     <row r="173" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="4"/>
@@ -3343,29 +5621,33 @@
       <c r="E173" s="4"/>
       <c r="F173" s="4"/>
       <c r="G173" s="11"/>
-      <c r="H173" s="11"/>
+      <c r="H173" s="14"/>
     </row>
     <row r="174" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="5" t="s">
+      <c r="A174" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B174" s="7" t="s">
+      <c r="B174" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C174" s="2" t="s">
+      <c r="C174" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="D174" s="6" t="s">
+      <c r="D174" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E174" s="8" t="s">
+      <c r="E174" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="F174" s="7" t="s">
+      <c r="F174" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G174" s="9"/>
-      <c r="H174" s="9"/>
+      <c r="G174" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="H174" s="12" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="175" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="3"/>
@@ -3375,7 +5657,7 @@
       <c r="E175" s="3"/>
       <c r="F175" s="3"/>
       <c r="G175" s="10"/>
-      <c r="H175" s="10"/>
+      <c r="H175" s="13"/>
     </row>
     <row r="176" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="3"/>
@@ -3385,7 +5667,7 @@
       <c r="E176" s="3"/>
       <c r="F176" s="3"/>
       <c r="G176" s="10"/>
-      <c r="H176" s="10"/>
+      <c r="H176" s="13"/>
     </row>
     <row r="177" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="4"/>
@@ -3395,29 +5677,33 @@
       <c r="E177" s="4"/>
       <c r="F177" s="4"/>
       <c r="G177" s="11"/>
-      <c r="H177" s="11"/>
+      <c r="H177" s="14"/>
     </row>
     <row r="178" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="5" t="s">
+      <c r="A178" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="B178" s="7" t="s">
+      <c r="B178" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C178" s="2" t="s">
+      <c r="C178" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="D178" s="6" t="s">
+      <c r="D178" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="E178" s="8" t="s">
+      <c r="E178" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F178" s="7" t="s">
+      <c r="F178" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G178" s="9"/>
-      <c r="H178" s="9"/>
+      <c r="G178" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="H178" s="12" t="s">
+        <v>284</v>
+      </c>
     </row>
     <row r="179" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="3"/>
@@ -3427,7 +5713,7 @@
       <c r="E179" s="3"/>
       <c r="F179" s="3"/>
       <c r="G179" s="10"/>
-      <c r="H179" s="10"/>
+      <c r="H179" s="13"/>
     </row>
     <row r="180" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="3"/>
@@ -3437,7 +5723,7 @@
       <c r="E180" s="3"/>
       <c r="F180" s="3"/>
       <c r="G180" s="10"/>
-      <c r="H180" s="10"/>
+      <c r="H180" s="13"/>
     </row>
     <row r="181" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="4"/>
@@ -3447,29 +5733,33 @@
       <c r="E181" s="4"/>
       <c r="F181" s="4"/>
       <c r="G181" s="11"/>
-      <c r="H181" s="11"/>
+      <c r="H181" s="14"/>
     </row>
     <row r="182" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="5" t="s">
+      <c r="A182" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="B182" s="7" t="s">
+      <c r="B182" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C182" s="2" t="s">
+      <c r="C182" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="D182" s="6" t="s">
+      <c r="D182" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E182" s="8" t="s">
+      <c r="E182" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="F182" s="7" t="s">
+      <c r="F182" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G182" s="9"/>
-      <c r="H182" s="9"/>
+      <c r="G182" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="H182" s="12" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="183" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="3"/>
@@ -3479,7 +5769,7 @@
       <c r="E183" s="3"/>
       <c r="F183" s="3"/>
       <c r="G183" s="10"/>
-      <c r="H183" s="10"/>
+      <c r="H183" s="13"/>
     </row>
     <row r="184" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="3"/>
@@ -3489,7 +5779,7 @@
       <c r="E184" s="3"/>
       <c r="F184" s="3"/>
       <c r="G184" s="10"/>
-      <c r="H184" s="10"/>
+      <c r="H184" s="13"/>
     </row>
     <row r="185" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="4"/>
@@ -3499,27 +5789,31 @@
       <c r="E185" s="4"/>
       <c r="F185" s="4"/>
       <c r="G185" s="11"/>
-      <c r="H185" s="11"/>
+      <c r="H185" s="14"/>
     </row>
     <row r="186" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="5" t="s">
+      <c r="A186" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="B186" s="7"/>
-      <c r="C186" s="2" t="s">
+      <c r="B186" s="5"/>
+      <c r="C186" s="8" t="s">
         <v>191</v>
       </c>
-      <c r="D186" s="6" t="s">
+      <c r="D186" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E186" s="8" t="s">
+      <c r="E186" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="F186" s="7" t="s">
+      <c r="F186" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G186" s="9"/>
-      <c r="H186" s="9"/>
+      <c r="G186" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="H186" s="12" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="187" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="3"/>
@@ -3529,7 +5823,7 @@
       <c r="E187" s="3"/>
       <c r="F187" s="3"/>
       <c r="G187" s="10"/>
-      <c r="H187" s="10"/>
+      <c r="H187" s="13"/>
     </row>
     <row r="188" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="3"/>
@@ -3539,7 +5833,7 @@
       <c r="E188" s="3"/>
       <c r="F188" s="3"/>
       <c r="G188" s="10"/>
-      <c r="H188" s="10"/>
+      <c r="H188" s="13"/>
     </row>
     <row r="189" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="4"/>
@@ -3549,29 +5843,33 @@
       <c r="E189" s="4"/>
       <c r="F189" s="4"/>
       <c r="G189" s="11"/>
-      <c r="H189" s="11"/>
+      <c r="H189" s="14"/>
     </row>
     <row r="190" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="5" t="s">
+      <c r="A190" s="7" t="s">
         <v>194</v>
       </c>
-      <c r="B190" s="7" t="s">
+      <c r="B190" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C190" s="2" t="s">
+      <c r="C190" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="D190" s="6" t="s">
+      <c r="D190" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E190" s="8" t="s">
+      <c r="E190" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="F190" s="7" t="s">
+      <c r="F190" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G190" s="9"/>
-      <c r="H190" s="9"/>
+      <c r="G190" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="H190" s="12" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="191" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="3"/>
@@ -3581,7 +5879,7 @@
       <c r="E191" s="3"/>
       <c r="F191" s="3"/>
       <c r="G191" s="10"/>
-      <c r="H191" s="10"/>
+      <c r="H191" s="13"/>
     </row>
     <row r="192" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="3"/>
@@ -3591,7 +5889,7 @@
       <c r="E192" s="3"/>
       <c r="F192" s="3"/>
       <c r="G192" s="10"/>
-      <c r="H192" s="10"/>
+      <c r="H192" s="13"/>
     </row>
     <row r="193" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="4"/>
@@ -3601,29 +5899,33 @@
       <c r="E193" s="4"/>
       <c r="F193" s="4"/>
       <c r="G193" s="11"/>
-      <c r="H193" s="11"/>
+      <c r="H193" s="14"/>
     </row>
     <row r="194" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="5" t="s">
+      <c r="A194" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="B194" s="7" t="s">
+      <c r="B194" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C194" s="2" t="s">
+      <c r="C194" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="D194" s="6" t="s">
+      <c r="D194" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E194" s="8" t="s">
+      <c r="E194" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="F194" s="7" t="s">
+      <c r="F194" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G194" s="9"/>
-      <c r="H194" s="9"/>
+      <c r="G194" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="H194" s="12" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="195" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="3"/>
@@ -3633,7 +5935,7 @@
       <c r="E195" s="3"/>
       <c r="F195" s="3"/>
       <c r="G195" s="10"/>
-      <c r="H195" s="10"/>
+      <c r="H195" s="13"/>
     </row>
     <row r="196" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="3"/>
@@ -3643,7 +5945,7 @@
       <c r="E196" s="3"/>
       <c r="F196" s="3"/>
       <c r="G196" s="10"/>
-      <c r="H196" s="10"/>
+      <c r="H196" s="13"/>
     </row>
     <row r="197" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="4"/>
@@ -3653,29 +5955,33 @@
       <c r="E197" s="4"/>
       <c r="F197" s="4"/>
       <c r="G197" s="11"/>
-      <c r="H197" s="11"/>
+      <c r="H197" s="14"/>
     </row>
     <row r="198" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="5" t="s">
+      <c r="A198" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="B198" s="7" t="s">
+      <c r="B198" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C198" s="2" t="s">
+      <c r="C198" s="8" t="s">
         <v>206</v>
       </c>
-      <c r="D198" s="6" t="s">
+      <c r="D198" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="E198" s="8" t="s">
+      <c r="E198" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="F198" s="7" t="s">
+      <c r="F198" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G198" s="9"/>
-      <c r="H198" s="9"/>
+      <c r="G198" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="H198" s="12" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="199" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="3"/>
@@ -3685,7 +5991,7 @@
       <c r="E199" s="3"/>
       <c r="F199" s="3"/>
       <c r="G199" s="10"/>
-      <c r="H199" s="10"/>
+      <c r="H199" s="13"/>
     </row>
     <row r="200" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="3"/>
@@ -3695,7 +6001,7 @@
       <c r="E200" s="3"/>
       <c r="F200" s="3"/>
       <c r="G200" s="10"/>
-      <c r="H200" s="10"/>
+      <c r="H200" s="13"/>
     </row>
     <row r="201" spans="1:8" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="4"/>
@@ -3705,7 +6011,7 @@
       <c r="E201" s="4"/>
       <c r="F201" s="4"/>
       <c r="G201" s="11"/>
-      <c r="H201" s="11"/>
+      <c r="H201" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="400">
@@ -3810,9 +6116,12 @@
     <mergeCell ref="G18:G21"/>
     <mergeCell ref="G22:G25"/>
     <mergeCell ref="C14:C17"/>
-    <mergeCell ref="B66:B69"/>
-    <mergeCell ref="C98:C101"/>
-    <mergeCell ref="C154:C157"/>
+    <mergeCell ref="F10:F13"/>
+    <mergeCell ref="F6:F9"/>
+    <mergeCell ref="C10:C13"/>
+    <mergeCell ref="E10:E13"/>
+    <mergeCell ref="E22:E25"/>
+    <mergeCell ref="D6:D9"/>
     <mergeCell ref="E14:E17"/>
     <mergeCell ref="A166:A169"/>
     <mergeCell ref="E102:E105"/>
@@ -3831,12 +6140,9 @@
     <mergeCell ref="D22:D25"/>
     <mergeCell ref="C26:C29"/>
     <mergeCell ref="A106:A109"/>
-    <mergeCell ref="F30:F33"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A54:A57"/>
-    <mergeCell ref="D46:D49"/>
-    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="E110:E113"/>
+    <mergeCell ref="A94:A97"/>
+    <mergeCell ref="A42:A45"/>
     <mergeCell ref="D198:D201"/>
     <mergeCell ref="A90:A93"/>
     <mergeCell ref="A146:A149"/>
@@ -3847,7 +6153,6 @@
     <mergeCell ref="A178:A181"/>
     <mergeCell ref="D126:D129"/>
     <mergeCell ref="C94:C97"/>
-    <mergeCell ref="A74:A77"/>
     <mergeCell ref="F126:F129"/>
     <mergeCell ref="D166:D169"/>
     <mergeCell ref="E94:E97"/>
@@ -3855,13 +6160,22 @@
     <mergeCell ref="F110:F113"/>
     <mergeCell ref="D150:D153"/>
     <mergeCell ref="E154:E157"/>
-    <mergeCell ref="E110:E113"/>
-    <mergeCell ref="F94:F97"/>
-    <mergeCell ref="B158:B161"/>
-    <mergeCell ref="D78:D81"/>
-    <mergeCell ref="F98:F101"/>
-    <mergeCell ref="C86:C89"/>
-    <mergeCell ref="F82:F85"/>
+    <mergeCell ref="C98:C101"/>
+    <mergeCell ref="C154:C157"/>
+    <mergeCell ref="E150:E153"/>
+    <mergeCell ref="F38:F41"/>
+    <mergeCell ref="F70:F73"/>
+    <mergeCell ref="E34:E37"/>
+    <mergeCell ref="D134:D137"/>
+    <mergeCell ref="B154:B157"/>
+    <mergeCell ref="F30:F33"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A54:A57"/>
+    <mergeCell ref="D46:D49"/>
+    <mergeCell ref="C54:C57"/>
+    <mergeCell ref="A74:A77"/>
+    <mergeCell ref="B66:B69"/>
     <mergeCell ref="D26:D29"/>
     <mergeCell ref="E130:E133"/>
     <mergeCell ref="D54:D57"/>
@@ -3869,6 +6183,8 @@
     <mergeCell ref="B30:B33"/>
     <mergeCell ref="C138:C141"/>
     <mergeCell ref="B38:B41"/>
+    <mergeCell ref="F146:F149"/>
+    <mergeCell ref="B122:B125"/>
     <mergeCell ref="A194:A197"/>
     <mergeCell ref="A46:A49"/>
     <mergeCell ref="F190:F193"/>
@@ -3893,11 +6209,6 @@
     <mergeCell ref="C102:C105"/>
     <mergeCell ref="B26:B29"/>
     <mergeCell ref="A34:A37"/>
-    <mergeCell ref="F10:F13"/>
-    <mergeCell ref="A94:A97"/>
-    <mergeCell ref="F146:F149"/>
-    <mergeCell ref="B122:B125"/>
-    <mergeCell ref="E150:E153"/>
     <mergeCell ref="D178:D181"/>
     <mergeCell ref="D34:D37"/>
     <mergeCell ref="F178:F181"/>
@@ -3917,6 +6228,11 @@
     <mergeCell ref="F46:F49"/>
     <mergeCell ref="B166:B169"/>
     <mergeCell ref="E74:E77"/>
+    <mergeCell ref="F62:F65"/>
+    <mergeCell ref="E86:E89"/>
+    <mergeCell ref="B74:B77"/>
+    <mergeCell ref="A170:A173"/>
+    <mergeCell ref="A114:A117"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="D2:D5"/>
     <mergeCell ref="B42:B45"/>
@@ -3941,7 +6257,6 @@
     <mergeCell ref="E70:E73"/>
     <mergeCell ref="C106:C109"/>
     <mergeCell ref="C46:C49"/>
-    <mergeCell ref="F62:F65"/>
     <mergeCell ref="B198:B201"/>
     <mergeCell ref="D14:D17"/>
     <mergeCell ref="F14:F17"/>
@@ -3966,10 +6281,6 @@
     <mergeCell ref="B78:B81"/>
     <mergeCell ref="F42:F45"/>
     <mergeCell ref="F154:F157"/>
-    <mergeCell ref="E86:E89"/>
-    <mergeCell ref="B74:B77"/>
-    <mergeCell ref="A170:A173"/>
-    <mergeCell ref="A114:A117"/>
     <mergeCell ref="C170:C173"/>
     <mergeCell ref="F78:F81"/>
     <mergeCell ref="F118:F121"/>
@@ -3989,6 +6300,11 @@
     <mergeCell ref="E138:E141"/>
     <mergeCell ref="D118:D121"/>
     <mergeCell ref="B118:B121"/>
+    <mergeCell ref="F170:F173"/>
+    <mergeCell ref="A154:A157"/>
+    <mergeCell ref="E162:E165"/>
+    <mergeCell ref="D130:D133"/>
+    <mergeCell ref="E166:E169"/>
     <mergeCell ref="C194:C197"/>
     <mergeCell ref="C38:C41"/>
     <mergeCell ref="D58:D61"/>
@@ -4013,13 +6329,6 @@
     <mergeCell ref="F138:F141"/>
     <mergeCell ref="C142:C145"/>
     <mergeCell ref="F90:F93"/>
-    <mergeCell ref="F170:F173"/>
-    <mergeCell ref="A154:A157"/>
-    <mergeCell ref="F38:F41"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="E162:E165"/>
-    <mergeCell ref="D130:D133"/>
-    <mergeCell ref="A14:A17"/>
     <mergeCell ref="F130:F133"/>
     <mergeCell ref="B162:B165"/>
     <mergeCell ref="A134:A137"/>
@@ -4034,25 +6343,16 @@
     <mergeCell ref="F66:F69"/>
     <mergeCell ref="D18:D21"/>
     <mergeCell ref="D146:D149"/>
-    <mergeCell ref="E166:E169"/>
     <mergeCell ref="A26:A29"/>
     <mergeCell ref="D158:D161"/>
-    <mergeCell ref="F6:F9"/>
     <mergeCell ref="F86:F89"/>
     <mergeCell ref="F142:F145"/>
-    <mergeCell ref="C10:C13"/>
     <mergeCell ref="B62:B65"/>
-    <mergeCell ref="E10:E13"/>
-    <mergeCell ref="B14:B17"/>
     <mergeCell ref="B70:B73"/>
     <mergeCell ref="D70:D73"/>
     <mergeCell ref="E98:E101"/>
-    <mergeCell ref="F70:F73"/>
-    <mergeCell ref="E34:E37"/>
-    <mergeCell ref="D134:D137"/>
-    <mergeCell ref="E22:E25"/>
-    <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="F94:F97"/>
+    <mergeCell ref="B158:B161"/>
     <mergeCell ref="F114:F117"/>
     <mergeCell ref="C118:C121"/>
     <mergeCell ref="C58:C61"/>
@@ -4063,11 +6363,10 @@
     <mergeCell ref="E54:E57"/>
     <mergeCell ref="D74:D77"/>
     <mergeCell ref="D114:D117"/>
-    <mergeCell ref="B154:B157"/>
-    <mergeCell ref="D6:D9"/>
-    <mergeCell ref="D190:D193"/>
-    <mergeCell ref="B86:B89"/>
-    <mergeCell ref="E82:E85"/>
+    <mergeCell ref="D78:D81"/>
+    <mergeCell ref="F98:F101"/>
+    <mergeCell ref="C86:C89"/>
+    <mergeCell ref="F82:F85"/>
     <mergeCell ref="A138:A141"/>
     <mergeCell ref="D86:D89"/>
     <mergeCell ref="B182:B185"/>
@@ -4088,6 +6387,10 @@
     <mergeCell ref="C6:C9"/>
     <mergeCell ref="C62:C65"/>
     <mergeCell ref="A98:A101"/>
+    <mergeCell ref="B10:B13"/>
+    <mergeCell ref="B98:B101"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="B14:B17"/>
     <mergeCell ref="D194:D197"/>
     <mergeCell ref="F134:F137"/>
     <mergeCell ref="E62:E65"/>
@@ -4109,7 +6412,11 @@
     <mergeCell ref="A190:A193"/>
     <mergeCell ref="C190:C193"/>
     <mergeCell ref="B114:B117"/>
+    <mergeCell ref="D190:D193"/>
+    <mergeCell ref="B86:B89"/>
+    <mergeCell ref="E82:E85"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>